--- a/budget/output/Фин.модель — Курортный.xlsx
+++ b/budget/output/Фин.модель — Курортный.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Текущий бюджет" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Цель 20% рент." sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Цель 15% рент." sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="+30% ФОТ → 20%" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="+40% ФОТ → 20%" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,6 +185,12 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1638,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1653,7 +1659,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финансовая модель — Живи в Курортном  |  Сценарий: цель ЧП 20%</t>
+          <t>Финансовая модель — Живи в Курортном  |  ФОТ +30%  →  цель ЧП 20%</t>
         </is>
       </c>
     </row>
@@ -1754,28 +1760,28 @@
       <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="22" t="n">
         <v>2071730</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="22" t="n">
         <v>1960608</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="22" t="n">
         <v>1960609</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="22" t="n">
         <v>1960609</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="22" t="n">
         <v>7953556</v>
       </c>
-      <c r="G6" s="21" t="n">
-        <v>9694210.06329114</v>
+      <c r="G6" s="23" t="n">
+        <v>12215818.9556962</v>
       </c>
     </row>
     <row r="7">
@@ -1826,7 +1832,7 @@
         <v>2690035</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2690035</v>
+        <v>3497045.5</v>
       </c>
     </row>
     <row r="10">
@@ -1851,7 +1857,7 @@
         <v>2400000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2400000</v>
+        <v>3120000</v>
       </c>
     </row>
     <row r="11">
@@ -1876,7 +1882,7 @@
         <v>299800</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>299800</v>
+        <v>389740</v>
       </c>
     </row>
     <row r="12">
@@ -1901,7 +1907,7 @@
         <v>112000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>112000</v>
+        <v>145600</v>
       </c>
     </row>
     <row r="13">
@@ -1926,7 +1932,7 @@
         <v>5501835</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>5501835</v>
+        <v>7152385.5</v>
       </c>
     </row>
     <row r="14">
@@ -1964,7 +1970,7 @@
         <v>440000</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>440000</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="16">
@@ -1989,7 +1995,7 @@
         <v>382200</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>382200</v>
+        <v>496860</v>
       </c>
     </row>
     <row r="17">
@@ -2014,7 +2020,7 @@
         <v>822200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>822200</v>
+        <v>1068860</v>
       </c>
     </row>
     <row r="18">
@@ -2039,7 +2045,7 @@
         <v>6324035</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>6324035</v>
+        <v>8221245.5</v>
       </c>
     </row>
     <row r="19">
@@ -2302,7 +2308,7 @@
         <v>6625547</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>6625547</v>
+        <v>8522757.5</v>
       </c>
     </row>
     <row r="30">
@@ -2327,7 +2333,7 @@
         <v>1328009</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>3068663.06329114</v>
+        <v>3693061.455696203</v>
       </c>
     </row>
     <row r="31">
@@ -2343,7 +2349,7 @@
       <c r="F31" s="16" t="inlineStr"/>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.2%</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2438,7 @@
         <v>771817</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>2512471.06329114</v>
+        <v>3136869.455696203</v>
       </c>
     </row>
     <row r="36">
@@ -2495,7 +2501,7 @@
         <v>378360</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>461629</v>
+        <v>581706</v>
       </c>
     </row>
     <row r="39">
@@ -2520,7 +2526,7 @@
         <v>490360</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>573629</v>
+        <v>693706</v>
       </c>
     </row>
     <row r="40">
@@ -2545,7 +2551,7 @@
         <v>281457</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>1938842</v>
+        <v>2443164</v>
       </c>
     </row>
     <row r="41">
@@ -2592,12 +2598,12 @@
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>Цель: рентабельность чистой прибыли</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>20%</t>
+          <t>Прирост ФОТ (+30%)</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>1,897,210 ₽</t>
         </is>
       </c>
       <c r="C45" s="19" t="n"/>
@@ -2609,12 +2615,12 @@
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Требуемая выручка для цели</t>
+          <t>Цель: рент. чистой прибыли</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>9,694,210 ₽</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
@@ -2626,14 +2632,10 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Необходимый прирост выручки</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>+1,740,654 ₽</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr"/>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="n"/>
@@ -2643,12 +2645,12 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Прирост контракта, %</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>+21.9%</t>
+          <t>Требуемая выручка (новый контракт)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>12,215,819 ₽</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
@@ -2660,12 +2662,12 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Требуемая МЕСЯЧНАЯ ставка</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>2,423,553 ₽/мес</t>
+          <t>Прирост выручки</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>+4,262,263 ₽</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
@@ -2677,12 +2679,12 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Текущая МЕСЯЧНАЯ ставка</t>
+          <t>Прирост контракта, %</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>1,988,389 ₽/мес</t>
+          <t>+53.6%</t>
         </is>
       </c>
       <c r="C50" s="19" t="n"/>
@@ -2694,19 +2696,96 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Текущая рентабельность ч.п.</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr"/>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Требуемая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>3,053,955 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Текущая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>1,988,389 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Прирост мес. ставки</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>+1,065,566 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr"/>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Рентабельность ЧП (сценарий)</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2723,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2738,7 +2817,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финансовая модель — Живи в Курортном  |  Сценарий: цель ЧП 15%</t>
+          <t>Финансовая модель — Живи в Курортном  |  ФОТ +40%  →  цель ЧП 20%</t>
         </is>
       </c>
     </row>
@@ -2839,28 +2918,28 @@
       <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>ИТОГО ВЫРУЧКА</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="22" t="n">
         <v>2071730</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="22" t="n">
         <v>1960608</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="22" t="n">
         <v>1960609</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="22" t="n">
         <v>1960609</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="22" t="n">
         <v>7953556</v>
       </c>
-      <c r="G6" s="21" t="n">
-        <v>9090119.821958458</v>
+      <c r="G6" s="23" t="n">
+        <v>13056355.25316456</v>
       </c>
     </row>
     <row r="7">
@@ -2911,7 +2990,7 @@
         <v>2690035</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2690035</v>
+        <v>3766049</v>
       </c>
     </row>
     <row r="10">
@@ -2936,7 +3015,7 @@
         <v>2400000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2400000</v>
+        <v>3360000</v>
       </c>
     </row>
     <row r="11">
@@ -2961,7 +3040,7 @@
         <v>299800</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>299800</v>
+        <v>419720</v>
       </c>
     </row>
     <row r="12">
@@ -2986,7 +3065,7 @@
         <v>112000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>112000</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="13">
@@ -3011,7 +3090,7 @@
         <v>5501835</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>5501835</v>
+        <v>7702568.999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3049,7 +3128,7 @@
         <v>440000</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>440000</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="16">
@@ -3074,7 +3153,7 @@
         <v>382200</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>382200</v>
+        <v>535080</v>
       </c>
     </row>
     <row r="17">
@@ -3099,7 +3178,7 @@
         <v>822200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>822200</v>
+        <v>1151080</v>
       </c>
     </row>
     <row r="18">
@@ -3124,7 +3203,7 @@
         <v>6324035</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>6324035</v>
+        <v>8853649</v>
       </c>
     </row>
     <row r="19">
@@ -3387,7 +3466,7 @@
         <v>6625547</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>6625547</v>
+        <v>9155161</v>
       </c>
     </row>
     <row r="30">
@@ -3412,7 +3491,7 @@
         <v>1328009</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>2464572.821958458</v>
+        <v>3901194.253164558</v>
       </c>
     </row>
     <row r="31">
@@ -3428,7 +3507,7 @@
       <c r="F31" s="16" t="inlineStr"/>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3596,7 @@
         <v>771817</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>1908380.821958458</v>
+        <v>3345002.253164558</v>
       </c>
     </row>
     <row r="36">
@@ -3580,7 +3659,7 @@
         <v>378360</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>432863</v>
+        <v>621731</v>
       </c>
     </row>
     <row r="39">
@@ -3605,7 +3684,7 @@
         <v>490360</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>544863</v>
+        <v>733731</v>
       </c>
     </row>
     <row r="40">
@@ -3630,7 +3709,7 @@
         <v>281457</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>1363518</v>
+        <v>2611271</v>
       </c>
     </row>
     <row r="41">
@@ -3646,7 +3725,7 @@
       <c r="F41" s="16" t="inlineStr"/>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3756,12 @@
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>Цель: рентабельность чистой прибыли</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>15%</t>
+          <t>Прирост ФОТ (+40%)</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>2,529,614 ₽</t>
         </is>
       </c>
       <c r="C45" s="19" t="n"/>
@@ -3694,12 +3773,12 @@
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Требуемая выручка для цели</t>
+          <t>Цель: рент. чистой прибыли</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>9,090,120 ₽</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
@@ -3711,14 +3790,10 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Необходимый прирост выручки</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>+1,136,564 ₽</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr"/>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="n"/>
@@ -3728,12 +3803,12 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Прирост контракта, %</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>+14.3%</t>
+          <t>Требуемая выручка (новый контракт)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>13,056,355 ₽</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
@@ -3745,12 +3820,12 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Требуемая МЕСЯЧНАЯ ставка</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>2,272,530 ₽/мес</t>
+          <t>Прирост выручки</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>+5,102,799 ₽</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
@@ -3762,12 +3837,12 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Текущая МЕСЯЧНАЯ ставка</t>
+          <t>Прирост контракта, %</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>1,988,389 ₽/мес</t>
+          <t>+64.2%</t>
         </is>
       </c>
       <c r="C50" s="19" t="n"/>
@@ -3779,19 +3854,96 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Текущая рентабельность ч.п.</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr"/>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Требуемая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>3,264,089 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Текущая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>1,988,389 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Прирост мес. ставки</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>+1,275,700 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr"/>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Рентабельность ЧП (сценарий)</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
